--- a/2025-SSE/GBR/train/gbr_log_target.xlsx
+++ b/2025-SSE/GBR/train/gbr_log_target.xlsx
@@ -5,41 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github_local\reproducible-workflows\2025-SSE\GBR\train\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\khw\sse\temp\remove_zeo\relax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF246FC-82AE-400A-A428-311FF8E1ABE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D88D7E1-F1D4-4AAE-9FFB-9D51F2122024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="13065" windowHeight="12450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_train" sheetId="1" r:id="rId1"/>
     <sheet name="data_test" sheetId="2" r:id="rId2"/>
-    <sheet name="importance" sheetId="3" r:id="rId3"/>
-    <sheet name="score" sheetId="4" r:id="rId4"/>
+    <sheet name="score" sheetId="4" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data_test!$A$1:$F$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Ytrain</t>
   </si>
@@ -51,192 +34,6 @@
   </si>
   <si>
     <t>Ytest_pre</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>Ag</t>
-  </si>
-  <si>
-    <t>Al</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Ba</t>
-  </si>
-  <si>
-    <t>Bi</t>
-  </si>
-  <si>
-    <t>Br</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Ca</t>
-  </si>
-  <si>
-    <t>Ce</t>
-  </si>
-  <si>
-    <t>Cl</t>
-  </si>
-  <si>
-    <t>Co</t>
-  </si>
-  <si>
-    <t>Cr</t>
-  </si>
-  <si>
-    <t>Cu</t>
-  </si>
-  <si>
-    <t>Er</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Fe</t>
-  </si>
-  <si>
-    <t>Ga</t>
-  </si>
-  <si>
-    <t>Gd</t>
-  </si>
-  <si>
-    <t>Ge</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Hf</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>In</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>La</t>
-  </si>
-  <si>
-    <t>Li</t>
-  </si>
-  <si>
-    <t>Lu</t>
-  </si>
-  <si>
-    <t>Mg</t>
-  </si>
-  <si>
-    <t>Mn</t>
-  </si>
-  <si>
-    <t>Mo</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Na</t>
-  </si>
-  <si>
-    <t>Nb</t>
-  </si>
-  <si>
-    <t>Nd</t>
-  </si>
-  <si>
-    <t>Ni</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Pb</t>
-  </si>
-  <si>
-    <t>Pr</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Sb</t>
-  </si>
-  <si>
-    <t>Sc</t>
-  </si>
-  <si>
-    <t>Se</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>Sm</t>
-  </si>
-  <si>
-    <t>Sn</t>
-  </si>
-  <si>
-    <t>Sr</t>
-  </si>
-  <si>
-    <t>Ta</t>
-  </si>
-  <si>
-    <t>Te</t>
-  </si>
-  <si>
-    <t>Ti</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Zn</t>
-  </si>
-  <si>
-    <t>Zr</t>
-  </si>
-  <si>
-    <t>Density (g/cm3)</t>
-  </si>
-  <si>
-    <t>POAV (cm3/g)</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
   </si>
   <si>
     <t>r2_train</t>
@@ -268,339 +65,12 @@
   <si>
     <t>spearman_p_test</t>
   </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>composition</t>
-  </si>
-  <si>
-    <t>(La0.55Li0.45)(Ti0.9Al0.1)O3</t>
-  </si>
-  <si>
-    <t>(La0.6Li0.4)(Ti0.8Al0.2)O3</t>
-  </si>
-  <si>
-    <t>(Li0.55Mg0.45)(Li0.445Mg0.055)Ti1.5O4</t>
-  </si>
-  <si>
-    <t>(Li0.826Mg0.174)(Li0.374Mg0.026Ti1.60)O4</t>
-  </si>
-  <si>
-    <t>Fe0.19La2.95Li5.57Zr2O12</t>
-  </si>
-  <si>
-    <t>La0.565Li0.305TiO3</t>
-  </si>
-  <si>
-    <t>La0.56Li0.33TiO3</t>
-  </si>
-  <si>
-    <t>La0.595Li0.215TiO3</t>
-  </si>
-  <si>
-    <t>La0.62Li0.14TiO3</t>
-  </si>
-  <si>
-    <t>La0.63Li0.11(Mg0.5W0.5)O3</t>
-  </si>
-  <si>
-    <t>La0.64Li0.08TiO3</t>
-  </si>
-  <si>
-    <t>Li(Ti0.4Sn1.6)(PO4)3</t>
-  </si>
-  <si>
-    <t>Li(Ti0.6Sn1.4)(PO4)3</t>
-  </si>
-  <si>
-    <t>Li0.02Na0.48La0.5Nb2O6</t>
-  </si>
-  <si>
-    <t>Li0.07Na0.43La0.5Nb2O6</t>
-  </si>
-  <si>
-    <t>Li0.2Na0.3La0.5Nb2O6</t>
-  </si>
-  <si>
-    <t>Li0.3Na0.2La0.5Nb2O6</t>
-  </si>
-  <si>
-    <t>Li1.1Al0.1Ti1.9(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.2Al0.2Ti1.8(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.3Al0.3Ge1.7(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.3Al0.3Ti1.7(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.4Al0.4Ge1.6(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.5Al0.5Ge1.5(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.5Al0.5Ti1.5(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.6Al0.6Ge1.4(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.7Al0.7Ge1.3(PO4)3</t>
-  </si>
-  <si>
-    <t>Li1.8Al0.8Ge1.2(PO4)3</t>
-  </si>
-  <si>
-    <t>Li10(Ge0.776Sn0.224)P2S12</t>
-  </si>
-  <si>
-    <t>Li10.5(Sn0.2Si0.8)1.5P1.5S12</t>
-  </si>
-  <si>
-    <t>Li10Ge0.66Sn0.33P2S12</t>
-  </si>
-  <si>
-    <t>Li10GeP2S12</t>
-  </si>
-  <si>
-    <t>Li10SnP2S12</t>
-  </si>
-  <si>
-    <t>Li2VCl4</t>
-  </si>
-  <si>
-    <t>Li3.333Mg0.333P2S6</t>
-  </si>
-  <si>
-    <t>Li3Fe(MoO4)3</t>
-  </si>
-  <si>
-    <t>Li4Ge0.50Sn0.50Se4</t>
-  </si>
-  <si>
-    <t>Li4GeS2Se2</t>
-  </si>
-  <si>
-    <t>Li4SnS2Se2</t>
-  </si>
-  <si>
-    <t>Li4SnSe4</t>
-  </si>
-  <si>
-    <t>Li5.4La3Nb1.8Y0.2O12</t>
-  </si>
-  <si>
-    <t>Li5.5La3Nb1.75Y0.25O12</t>
-  </si>
-  <si>
-    <t>Li5.5La3Ta1.75Sm0.25O12</t>
-  </si>
-  <si>
-    <t>Li5.70La3Ta1.65Sm0.35O12</t>
-  </si>
-  <si>
-    <t>Li5.74La3Zr1.5Ta0.5O12</t>
-  </si>
-  <si>
-    <t>Li5.90La3Ta1.55Sm0.45O12</t>
-  </si>
-  <si>
-    <t>Li5AlO4</t>
-  </si>
-  <si>
-    <t>Li5La3Sb2O12</t>
-  </si>
-  <si>
-    <t>Li5La3Ta2O12</t>
-  </si>
-  <si>
-    <t>Li6.025P0.975Si0.025S5Br</t>
-  </si>
-  <si>
-    <t>Li6.05P0.95Si0.05S5Br</t>
-  </si>
-  <si>
-    <t>Li6.075P0.925Si0.075S5Br</t>
-  </si>
-  <si>
-    <t>Li6.10La3Ta1.45Sm0.55O12</t>
-  </si>
-  <si>
-    <t>Li6.125P0.875Si0.125S5Br</t>
-  </si>
-  <si>
-    <t>Li6.175P0.825Si0.175S5Br</t>
-  </si>
-  <si>
-    <t>Li6.1P0.95Si0.1S5Br</t>
-  </si>
-  <si>
-    <t>Li6.225P0.775Si0.225S5Br</t>
-  </si>
-  <si>
-    <t>Li6.25P0.75Si0.25S5Br</t>
-  </si>
-  <si>
-    <t>Li6.2La3Zr1.2Ta0.8O12</t>
-  </si>
-  <si>
-    <t>Li6.2P0.8Si0.2S5Br</t>
-  </si>
-  <si>
-    <t>Li6.35P0.65Si0.35S5Br</t>
-  </si>
-  <si>
-    <t>Li6.3P0.7Si0.3S5Br</t>
-  </si>
-  <si>
-    <t>Li6.4La3Zr1.4Ta0.6O12</t>
-  </si>
-  <si>
-    <t>Li6.5La3Nb1.25Y0.75O12</t>
-  </si>
-  <si>
-    <t>Li6.5La3Zr1.5Ta0.5O12</t>
-  </si>
-  <si>
-    <t>Li6.6La3Zr1.6Ta0.4O12</t>
-  </si>
-  <si>
-    <t>Li6.6P0.4Ge0.6S5I</t>
-  </si>
-  <si>
-    <t>Li6.75La3Zr1.75Ta0.25O12</t>
-  </si>
-  <si>
-    <t>Li6.7P0.3Ge0.7S5I</t>
-  </si>
-  <si>
-    <t>Li6.8La3Zr1.8Ta0.2O12</t>
-  </si>
-  <si>
-    <t>Li6BaLa2Ta2O12</t>
-  </si>
-  <si>
-    <t>Li6CaLa2Ta2O12</t>
-  </si>
-  <si>
-    <t>Li6CoCl8</t>
-  </si>
-  <si>
-    <t>Li6La3Nb1.5Y0.5O12</t>
-  </si>
-  <si>
-    <t>Li6P(S4.2Se0.8)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4.3Se0.7)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4.4Se0.6)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4.5Se0.5)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4.6Se0.4)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4.7Se0.3)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4.9Se0.1)Br</t>
-  </si>
-  <si>
-    <t>Li6P(S4Se)Br</t>
-  </si>
-  <si>
-    <t>Li6PS5Br</t>
-  </si>
-  <si>
-    <t>Li6PS5Br0.75I0.25</t>
-  </si>
-  <si>
-    <t>Li6PS5Cl0.75Br0.25</t>
-  </si>
-  <si>
-    <t>Li6PS5I</t>
-  </si>
-  <si>
-    <t>Li7La3Zr2O12</t>
-  </si>
-  <si>
-    <t>Li8GeP4</t>
-  </si>
-  <si>
-    <t>Li9.81Sn0.81P2.19S12</t>
-  </si>
-  <si>
-    <t>LiGe2(PO4)3</t>
-  </si>
-  <si>
-    <t>LiTi2(PO4)3</t>
-  </si>
-  <si>
-    <t>Family</t>
-  </si>
-  <si>
-    <t>argyrodites</t>
-  </si>
-  <si>
-    <t>cholorides</t>
-  </si>
-  <si>
-    <t>garnet</t>
-  </si>
-  <si>
-    <t>LGPS</t>
-  </si>
-  <si>
-    <t>LISICON</t>
-  </si>
-  <si>
-    <t>molybdates</t>
-  </si>
-  <si>
-    <t>NASICON</t>
-  </si>
-  <si>
-    <t>oxides</t>
-  </si>
-  <si>
-    <t>perovskites</t>
-  </si>
-  <si>
-    <t>phosphates</t>
-  </si>
-  <si>
-    <t>Rocksalt</t>
-  </si>
-  <si>
-    <t>thio-phosphate</t>
-  </si>
-  <si>
-    <t>sulfide</t>
-  </si>
-  <si>
-    <t>oxide</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,13 +82,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -656,28 +119,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4209,2985 +3660,865 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2">
         <v>-2.8210230529999998</v>
       </c>
-      <c r="D2">
+      <c r="B2">
         <v>-3.3516323566436772</v>
       </c>
-      <c r="E2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3">
         <v>-3.2456516639999999</v>
       </c>
-      <c r="D3">
+      <c r="B3">
         <v>-3.873120784759521</v>
       </c>
-      <c r="E3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4">
         <v>-10.815308569999999</v>
       </c>
-      <c r="D4">
+      <c r="B4">
         <v>-9.8748674392700195</v>
       </c>
-      <c r="E4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5">
         <v>-8.3726341430000009</v>
       </c>
-      <c r="D5">
+      <c r="B5">
         <v>-8.2307338714599609</v>
       </c>
-      <c r="E5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6">
         <v>-2.8601209139999999</v>
       </c>
-      <c r="D6">
+      <c r="B6">
         <v>-2.9544308185577388</v>
       </c>
-      <c r="E6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7">
         <v>-3.0190880619999998</v>
       </c>
-      <c r="D7">
+      <c r="B7">
         <v>-3.0680503845214839</v>
       </c>
-      <c r="E7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
         <v>-3.175223538</v>
       </c>
-      <c r="D8">
+      <c r="B8">
         <v>-3.0680503845214839</v>
       </c>
-      <c r="E8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9">
         <v>-3.0690509690000001</v>
       </c>
-      <c r="D9">
+      <c r="B9">
         <v>-3.3726568222045898</v>
       </c>
-      <c r="E9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9">
-        <f>ABS(C9-D9)</f>
-        <v>0.30360585320458977</v>
-      </c>
-      <c r="H9">
-        <f>AVERAGE(G9:G65)</f>
-        <v>0.47904883137998022</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10">
         <v>-3.354577731</v>
       </c>
-      <c r="D10">
+      <c r="B10">
         <v>-3.370073556900024</v>
       </c>
-      <c r="E10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10">
-        <f t="shared" ref="G10:G65" si="0">ABS(C10-D10)</f>
-        <v>1.5495825900023963E-2</v>
-      </c>
-      <c r="H10">
-        <f>AVERAGE(G66:G102)</f>
-        <v>0.55864230064363729</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>43</v>
-      </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11">
         <v>-5.1674910870000001</v>
       </c>
-      <c r="D11">
+      <c r="B11">
         <v>-5.7285213470458984</v>
       </c>
-      <c r="E11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>0.56103026004589829</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12">
         <v>-3.474955193</v>
       </c>
-      <c r="D12">
+      <c r="B12">
         <v>-3.7911033630371089</v>
       </c>
-      <c r="E12" t="s">
-        <v>177</v>
-      </c>
-      <c r="F12" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>0.31614817003710893</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13">
         <v>-5.5016894460000003</v>
       </c>
-      <c r="D13">
+      <c r="B13">
         <v>-7.1598572731018066</v>
       </c>
-      <c r="E13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F13" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>1.6581678271018063</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14">
         <v>-5.0259490969999998</v>
       </c>
-      <c r="D14">
+      <c r="B14">
         <v>-6.6820235252380371</v>
       </c>
-      <c r="E14" t="s">
-        <v>175</v>
-      </c>
-      <c r="F14" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>1.6560744282380373</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>54</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15">
         <v>-5.399027104</v>
       </c>
-      <c r="D15">
+      <c r="B15">
         <v>-4.9045209884643546</v>
       </c>
-      <c r="E15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F15" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
-        <v>0.49450611553564539</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>56</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16">
         <v>-4.9100948889999998</v>
       </c>
-      <c r="D16">
+      <c r="B16">
         <v>-4.9654040336608887</v>
       </c>
-      <c r="E16" t="s">
-        <v>177</v>
-      </c>
-      <c r="F16" t="s">
-        <v>182</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
-        <v>5.5309144660888876E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>63</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17">
         <v>-4.9281179929999999</v>
       </c>
-      <c r="D17">
+      <c r="B17">
         <v>-4.8294930458068848</v>
       </c>
-      <c r="E17" t="s">
-        <v>177</v>
-      </c>
-      <c r="F17" t="s">
-        <v>182</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>9.8624947193115098E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>66</v>
-      </c>
-      <c r="B18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18">
         <v>-4.9546770210000002</v>
       </c>
-      <c r="D18">
+      <c r="B18">
         <v>-4.8113594055175781</v>
       </c>
-      <c r="E18" t="s">
-        <v>177</v>
-      </c>
-      <c r="F18" t="s">
-        <v>182</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="0"/>
-        <v>0.14331761548242206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>87</v>
-      </c>
-      <c r="B19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19">
         <v>-4.5228787449999999</v>
       </c>
-      <c r="D19">
+      <c r="B19">
         <v>-3.1602237224578862</v>
       </c>
-      <c r="E19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="0"/>
-        <v>1.3626550225421137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>92</v>
-      </c>
-      <c r="B20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20">
         <v>-3.2254830339999998</v>
       </c>
-      <c r="D20">
+      <c r="B20">
         <v>-2.8634319305419922</v>
       </c>
-      <c r="E20" t="s">
-        <v>175</v>
-      </c>
-      <c r="F20" t="s">
-        <v>182</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="0"/>
-        <v>0.36205110345800762</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>93</v>
-      </c>
-      <c r="B21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21">
         <v>-2.4710833000000001</v>
       </c>
-      <c r="D21">
+      <c r="B21">
         <v>-2.977364301681519</v>
       </c>
-      <c r="E21" t="s">
-        <v>175</v>
-      </c>
-      <c r="F21" t="s">
-        <v>182</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="0"/>
-        <v>0.50628100168151891</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>103</v>
-      </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22">
         <v>-4.0840727880000003</v>
       </c>
-      <c r="D22">
+      <c r="B22">
         <v>-4.4498324394226074</v>
       </c>
-      <c r="E22" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>0.36575965142260713</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23">
         <v>-3.1414628019999999</v>
       </c>
-      <c r="D23">
+      <c r="B23">
         <v>-3.1605768203735352</v>
       </c>
-      <c r="E23" t="s">
-        <v>175</v>
-      </c>
-      <c r="F23" t="s">
-        <v>182</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="0"/>
-        <v>1.9114018373535213E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>105</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24">
         <v>-2.946921557</v>
       </c>
-      <c r="D24">
+      <c r="B24">
         <v>-3.539348840713501</v>
       </c>
-      <c r="E24" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" t="s">
-        <v>182</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
-        <v>0.59242728371350095</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>107</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25">
         <v>-2.9172146300000001</v>
       </c>
-      <c r="D25">
+      <c r="B25">
         <v>-3.014426708221436</v>
       </c>
-      <c r="E25" t="s">
-        <v>175</v>
-      </c>
-      <c r="F25" t="s">
-        <v>182</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="0"/>
-        <v>9.7212078221435849E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26">
         <v>-3.7258421510000002</v>
       </c>
-      <c r="D26">
+      <c r="B26">
         <v>-4.3951892852783203</v>
       </c>
-      <c r="E26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F26" t="s">
-        <v>182</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="0"/>
-        <v>0.66934713427832015</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>126</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27">
         <v>-3.4736607230000001</v>
       </c>
-      <c r="D27">
+      <c r="B27">
         <v>-4.3369464874267578</v>
       </c>
-      <c r="E27" t="s">
-        <v>175</v>
-      </c>
-      <c r="F27" t="s">
-        <v>182</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="0"/>
-        <v>0.86328576442675775</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>128</v>
-      </c>
-      <c r="B28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28">
         <v>-3.6055483189999999</v>
       </c>
-      <c r="D28">
+      <c r="B28">
         <v>-3.3738515377044682</v>
       </c>
-      <c r="E28" t="s">
-        <v>175</v>
-      </c>
-      <c r="F28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="0"/>
-        <v>0.23169678129553173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>142</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29">
         <v>-3.54668166</v>
       </c>
-      <c r="D29">
+      <c r="B29">
         <v>-4.3309535980224609</v>
       </c>
-      <c r="E29" t="s">
-        <v>175</v>
-      </c>
-      <c r="F29" t="s">
-        <v>182</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="0"/>
-        <v>0.78427193802246098</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>145</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30">
         <v>-3.578396073</v>
       </c>
-      <c r="D30">
+      <c r="B30">
         <v>-4.2953295707702637</v>
       </c>
-      <c r="E30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" t="s">
-        <v>182</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="0"/>
-        <v>0.71693349777026372</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>148</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31">
         <v>-3.8632794330000002</v>
       </c>
-      <c r="D31">
+      <c r="B31">
         <v>-4.1996803283691406</v>
       </c>
-      <c r="E31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F31" t="s">
-        <v>182</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="0"/>
-        <v>0.33640089536914042</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>153</v>
-      </c>
-      <c r="B32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32">
         <v>-1.850780887</v>
       </c>
-      <c r="D32">
+      <c r="B32">
         <v>-1.94404125213623</v>
       </c>
-      <c r="E32" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" t="s">
-        <v>181</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="0"/>
-        <v>9.3260365136230039E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>158</v>
-      </c>
-      <c r="B33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33">
         <v>-2.0560111249999999</v>
       </c>
-      <c r="D33">
+      <c r="B33">
         <v>-2.0914871692657471</v>
       </c>
-      <c r="E33" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" t="s">
-        <v>181</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="0"/>
-        <v>3.5476044265747131E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>160</v>
-      </c>
-      <c r="B34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34">
         <v>-2.193820026</v>
       </c>
-      <c r="D34">
+      <c r="B34">
         <v>-2.1044960021972661</v>
       </c>
-      <c r="E34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F34" t="s">
-        <v>181</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="0"/>
-        <v>8.9324023802733965E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>161</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35">
         <v>-1.9172146299999999</v>
       </c>
-      <c r="D35">
+      <c r="B35">
         <v>-1.9103759527206421</v>
       </c>
-      <c r="E35" t="s">
-        <v>172</v>
-      </c>
-      <c r="F35" t="s">
-        <v>181</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="0"/>
-        <v>6.8386772793578299E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>162</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36">
         <v>-1.609064893</v>
       </c>
-      <c r="D36">
+      <c r="B36">
         <v>-1.9096794128417971</v>
       </c>
-      <c r="E36" t="s">
-        <v>172</v>
-      </c>
-      <c r="F36" t="s">
-        <v>181</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="0"/>
-        <v>0.3006145198417971</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>163</v>
-      </c>
-      <c r="B37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37">
         <v>-2.119186408</v>
       </c>
-      <c r="D37">
+      <c r="B37">
         <v>-2.0933411121368408</v>
       </c>
-      <c r="E37" t="s">
-        <v>172</v>
-      </c>
-      <c r="F37" t="s">
-        <v>181</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="0"/>
-        <v>2.5845295863159201E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>166</v>
-      </c>
-      <c r="B38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38">
         <v>-2.4001169280000001</v>
       </c>
-      <c r="D38">
+      <c r="B38">
         <v>-2.1223781108856201</v>
       </c>
-      <c r="E38" t="s">
-        <v>172</v>
-      </c>
-      <c r="F38" t="s">
-        <v>181</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="0"/>
-        <v>0.27773881711437998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>167</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39">
         <v>-2.420216403</v>
       </c>
-      <c r="D39">
+      <c r="B39">
         <v>-2.1642858982086182</v>
       </c>
-      <c r="E39" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" t="s">
-        <v>181</v>
-      </c>
-      <c r="G39">
-        <f t="shared" si="0"/>
-        <v>0.2559305047913818</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>207</v>
-      </c>
-      <c r="B40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40">
         <v>-5.1580151949999999</v>
       </c>
-      <c r="D40">
+      <c r="B40">
         <v>-7.3012490272521973</v>
       </c>
-      <c r="E40" t="s">
-        <v>170</v>
-      </c>
-      <c r="F40" t="s">
-        <v>183</v>
-      </c>
-      <c r="G40">
-        <f t="shared" si="0"/>
-        <v>2.1432338322521973</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>218</v>
-      </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41">
         <v>-7.0861861480000004</v>
       </c>
-      <c r="D41">
+      <c r="B41">
         <v>-5.7360563278198242</v>
       </c>
-      <c r="E41" t="s">
-        <v>180</v>
-      </c>
-      <c r="F41" t="s">
-        <v>181</v>
-      </c>
-      <c r="G41">
-        <f t="shared" si="0"/>
-        <v>1.3501298201801761</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>247</v>
-      </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42">
         <v>-9.2298847049999999</v>
       </c>
-      <c r="D42">
+      <c r="B42">
         <v>-8.6215143203735352</v>
       </c>
-      <c r="E42" t="s">
-        <v>174</v>
-      </c>
-      <c r="F42" t="s">
-        <v>182</v>
-      </c>
-      <c r="G42">
-        <f t="shared" si="0"/>
-        <v>0.60837038462646476</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>281</v>
-      </c>
-      <c r="B43" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43">
         <v>-5.7447274950000002</v>
       </c>
-      <c r="D43">
+      <c r="B43">
         <v>-5.306645393371582</v>
       </c>
-      <c r="E43" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" t="s">
-        <v>183</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="0"/>
-        <v>0.43808210162841821</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>284</v>
-      </c>
-      <c r="B44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44">
         <v>-4.5528419690000002</v>
       </c>
-      <c r="D44">
+      <c r="B44">
         <v>-4.6553058624267578</v>
       </c>
-      <c r="E44" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" t="s">
-        <v>183</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="0"/>
-        <v>0.10246389342675766</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>295</v>
-      </c>
-      <c r="B45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45">
         <v>-4.4436974989999998</v>
       </c>
-      <c r="D45">
+      <c r="B45">
         <v>-6.0313272476196289</v>
       </c>
-      <c r="E45" t="s">
-        <v>173</v>
-      </c>
-      <c r="F45" t="s">
-        <v>183</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="0"/>
-        <v>1.5876297486196291</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>299</v>
-      </c>
-      <c r="B46" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46">
         <v>-4.6989700040000004</v>
       </c>
-      <c r="D46">
+      <c r="B46">
         <v>-6.853095531463623</v>
       </c>
-      <c r="E46" t="s">
-        <v>173</v>
-      </c>
-      <c r="F46" t="s">
-        <v>183</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="0"/>
-        <v>2.1541255274636226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>307</v>
-      </c>
-      <c r="B47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47">
         <v>-4.1713401030000004</v>
       </c>
-      <c r="D47">
+      <c r="B47">
         <v>-4.3201999664306641</v>
       </c>
-      <c r="E47" t="s">
-        <v>171</v>
-      </c>
-      <c r="F47" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="0"/>
-        <v>0.14885986343066371</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>310</v>
-      </c>
-      <c r="B48" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48">
         <v>-4.0371573190000003</v>
       </c>
-      <c r="D48">
+      <c r="B48">
         <v>-4.2284073829650879</v>
       </c>
-      <c r="E48" t="s">
-        <v>171</v>
-      </c>
-      <c r="F48" t="s">
-        <v>182</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="0"/>
-        <v>0.19125006396508759</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>311</v>
-      </c>
-      <c r="B49" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49">
         <v>-5.2865094570000002</v>
       </c>
-      <c r="D49">
+      <c r="B49">
         <v>-4.9842405319213867</v>
       </c>
-      <c r="E49" t="s">
-        <v>171</v>
-      </c>
-      <c r="F49" t="s">
-        <v>182</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="0"/>
-        <v>0.30226892507861347</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>312</v>
-      </c>
-      <c r="B50" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50">
         <v>-4.6675615400000003</v>
       </c>
-      <c r="D50">
+      <c r="B50">
         <v>-5.012392520904541</v>
       </c>
-      <c r="E50" t="s">
-        <v>171</v>
-      </c>
-      <c r="F50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G50">
-        <f t="shared" si="0"/>
-        <v>0.34483098090454067</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>313</v>
-      </c>
-      <c r="B51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51">
         <v>-3.0443122499999999</v>
       </c>
-      <c r="D51">
+      <c r="B51">
         <v>-3.2651667594909668</v>
       </c>
-      <c r="E51" t="s">
-        <v>171</v>
-      </c>
-      <c r="F51" t="s">
-        <v>182</v>
-      </c>
-      <c r="G51">
-        <f t="shared" si="0"/>
-        <v>0.22085450949096685</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>314</v>
-      </c>
-      <c r="B52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52">
         <v>-4.9281179929999999</v>
       </c>
-      <c r="D52">
+      <c r="B52">
         <v>-4.8328371047973633</v>
       </c>
-      <c r="E52" t="s">
-        <v>171</v>
-      </c>
-      <c r="F52" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="0"/>
-        <v>9.5280888202636582E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>316</v>
-      </c>
-      <c r="B53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C53">
         <v>-9.3010299960000005</v>
       </c>
-      <c r="D53">
+      <c r="B53">
         <v>-8.1085243225097656</v>
       </c>
-      <c r="E53" t="s">
-        <v>176</v>
-      </c>
-      <c r="F53" t="s">
-        <v>182</v>
-      </c>
-      <c r="G53">
-        <f t="shared" si="0"/>
-        <v>1.1925056734902348</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>324</v>
-      </c>
-      <c r="B54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54">
         <v>-5.477555766</v>
       </c>
-      <c r="D54">
+      <c r="B54">
         <v>-5.0464143753051758</v>
       </c>
-      <c r="E54" t="s">
-        <v>171</v>
-      </c>
-      <c r="F54" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54">
-        <f t="shared" si="0"/>
-        <v>0.43114139069482427</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>327</v>
-      </c>
-      <c r="B55" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55">
         <v>-4.7986028760000004</v>
       </c>
-      <c r="D55">
+      <c r="B55">
         <v>-5.0243053436279297</v>
       </c>
-      <c r="E55" t="s">
-        <v>171</v>
-      </c>
-      <c r="F55" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="0"/>
-        <v>0.22570246762792934</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>333</v>
-      </c>
-      <c r="B56" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56">
         <v>-3.0565054840000001</v>
       </c>
-      <c r="D56">
+      <c r="B56">
         <v>-3.252030611038208</v>
       </c>
-      <c r="E56" t="s">
-        <v>169</v>
-      </c>
-      <c r="F56" t="s">
-        <v>181</v>
-      </c>
-      <c r="G56">
-        <f t="shared" si="0"/>
-        <v>0.1955251270382079</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>335</v>
-      </c>
-      <c r="B57" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57">
         <v>-3.359518563</v>
       </c>
-      <c r="D57">
+      <c r="B57">
         <v>-2.8798930644989009</v>
       </c>
-      <c r="E57" t="s">
-        <v>169</v>
-      </c>
-      <c r="F57" t="s">
-        <v>181</v>
-      </c>
-      <c r="G57">
-        <f t="shared" si="0"/>
-        <v>0.47962549850109903</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>336</v>
-      </c>
-      <c r="B58" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58">
         <v>-3.0589857559999998</v>
       </c>
-      <c r="D58">
+      <c r="B58">
         <v>-2.8405592441558838</v>
       </c>
-      <c r="E58" t="s">
-        <v>169</v>
-      </c>
-      <c r="F58" t="s">
-        <v>181</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="0"/>
-        <v>0.21842651184411599</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>337</v>
-      </c>
-      <c r="B59" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59">
         <v>-4.8538719639999997</v>
       </c>
-      <c r="D59">
+      <c r="B59">
         <v>-4.672454833984375</v>
       </c>
-      <c r="E59" t="s">
-        <v>171</v>
-      </c>
-      <c r="F59" t="s">
-        <v>182</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="0"/>
-        <v>0.18141713001562465</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>339</v>
-      </c>
-      <c r="B60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60">
         <v>-3.0447934619999999</v>
       </c>
-      <c r="D60">
+      <c r="B60">
         <v>-2.782909631729126</v>
       </c>
-      <c r="E60" t="s">
-        <v>169</v>
-      </c>
-      <c r="F60" t="s">
-        <v>181</v>
-      </c>
-      <c r="G60">
-        <f t="shared" si="0"/>
-        <v>0.26188383027087392</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>340</v>
-      </c>
-      <c r="B61" t="s">
-        <v>131</v>
-      </c>
-      <c r="C61">
         <v>-3.0310503190000002</v>
       </c>
-      <c r="D61">
+      <c r="B61">
         <v>-2.7903823852539058</v>
       </c>
-      <c r="E61" t="s">
-        <v>169</v>
-      </c>
-      <c r="F61" t="s">
-        <v>181</v>
-      </c>
-      <c r="G61">
-        <f t="shared" si="0"/>
-        <v>0.24066793374609441</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>341</v>
-      </c>
-      <c r="B62" t="s">
-        <v>132</v>
-      </c>
-      <c r="C62">
         <v>-3.0974532209999999</v>
       </c>
-      <c r="D62">
+      <c r="B62">
         <v>-2.7946057319641109</v>
       </c>
-      <c r="E62" t="s">
-        <v>169</v>
-      </c>
-      <c r="F62" t="s">
-        <v>181</v>
-      </c>
-      <c r="G62">
-        <f t="shared" si="0"/>
-        <v>0.30284748903588898</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>343</v>
-      </c>
-      <c r="B63" t="s">
-        <v>133</v>
-      </c>
-      <c r="C63">
         <v>-2.9665762450000002</v>
       </c>
-      <c r="D63">
+      <c r="B63">
         <v>-2.7775671482086182</v>
       </c>
-      <c r="E63" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" t="s">
-        <v>181</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="0"/>
-        <v>0.189009096791382</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>346</v>
-      </c>
-      <c r="B64" t="s">
-        <v>134</v>
-      </c>
-      <c r="C64">
         <v>-2.850780887</v>
       </c>
-      <c r="D64">
+      <c r="B64">
         <v>-2.6282846927642818</v>
       </c>
-      <c r="E64" t="s">
-        <v>169</v>
-      </c>
-      <c r="F64" t="s">
-        <v>181</v>
-      </c>
-      <c r="G64">
-        <f t="shared" si="0"/>
-        <v>0.2224961942357182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>349</v>
-      </c>
-      <c r="B65" t="s">
-        <v>135</v>
-      </c>
-      <c r="C65">
         <v>-3.4948500220000001</v>
       </c>
-      <c r="D65">
+      <c r="B65">
         <v>-3.6772599220275879</v>
       </c>
-      <c r="E65" t="s">
-        <v>171</v>
-      </c>
-      <c r="F65" t="s">
-        <v>182</v>
-      </c>
-      <c r="G65">
-        <f t="shared" si="0"/>
-        <v>0.18240990002758783</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>350</v>
-      </c>
-      <c r="B66" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66">
         <v>-2.772113295</v>
       </c>
-      <c r="D66">
+      <c r="B66">
         <v>-2.7635118961334229</v>
       </c>
-      <c r="E66" t="s">
-        <v>169</v>
-      </c>
-      <c r="F66" t="s">
-        <v>181</v>
-      </c>
-      <c r="G66">
-        <f>ABS(C66-D66)</f>
-        <v>8.6013988665771812E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>351</v>
-      </c>
-      <c r="B67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67">
         <v>-2.6307841430000001</v>
       </c>
-      <c r="D67">
+      <c r="B67">
         <v>-2.5954833030700679</v>
       </c>
-      <c r="E67" t="s">
-        <v>169</v>
-      </c>
-      <c r="F67" t="s">
-        <v>181</v>
-      </c>
-      <c r="G67">
-        <f t="shared" ref="G67:G102" si="1">ABS(C67-D67)</f>
-        <v>3.530083992993216E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>352</v>
-      </c>
-      <c r="B68" t="s">
-        <v>138</v>
-      </c>
-      <c r="C68">
         <v>-2.782516056</v>
       </c>
-      <c r="D68">
+      <c r="B68">
         <v>-2.6586718559265141</v>
       </c>
-      <c r="E68" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" t="s">
-        <v>181</v>
-      </c>
-      <c r="G68">
-        <f t="shared" si="1"/>
-        <v>0.12384420007348584</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>354</v>
-      </c>
-      <c r="B69" t="s">
-        <v>139</v>
-      </c>
-      <c r="C69">
         <v>-3</v>
       </c>
-      <c r="D69">
+      <c r="B69">
         <v>-3.703696489334106</v>
       </c>
-      <c r="E69" t="s">
-        <v>171</v>
-      </c>
-      <c r="F69" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69">
-        <f t="shared" si="1"/>
-        <v>0.703696489334106</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>357</v>
-      </c>
-      <c r="B70" t="s">
-        <v>140</v>
-      </c>
-      <c r="C70">
         <v>-3.5686362360000001</v>
       </c>
-      <c r="D70">
+      <c r="B70">
         <v>-4.1414070129394531</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F70" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70">
-        <f t="shared" si="1"/>
-        <v>0.572770776939453</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>358</v>
-      </c>
-      <c r="B71" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71">
         <v>-3.5528419690000002</v>
       </c>
-      <c r="D71">
+      <c r="B71">
         <v>-3.472215890884399</v>
       </c>
-      <c r="E71" t="s">
-        <v>171</v>
-      </c>
-      <c r="F71" t="s">
-        <v>182</v>
-      </c>
-      <c r="G71">
-        <f t="shared" si="1"/>
-        <v>8.0626078115601185E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>364</v>
-      </c>
-      <c r="B72" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72">
         <v>-3.3279021420000001</v>
       </c>
-      <c r="D72">
+      <c r="B72">
         <v>-3.322291374206543</v>
       </c>
-      <c r="E72" t="s">
-        <v>171</v>
-      </c>
-      <c r="F72" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72">
-        <f t="shared" si="1"/>
-        <v>5.6107677934571498E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>365</v>
-      </c>
-      <c r="B73" t="s">
-        <v>143</v>
-      </c>
-      <c r="C73">
         <v>-2.2831622770000002</v>
       </c>
-      <c r="D73">
+      <c r="B73">
         <v>-3.5526671409606929</v>
       </c>
-      <c r="E73" t="s">
-        <v>169</v>
-      </c>
-      <c r="F73" t="s">
-        <v>181</v>
-      </c>
-      <c r="G73">
-        <f t="shared" si="1"/>
-        <v>1.2695048639606927</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>367</v>
-      </c>
-      <c r="B74" t="s">
-        <v>144</v>
-      </c>
-      <c r="C74">
         <v>-3.0604807470000002</v>
       </c>
-      <c r="D74">
+      <c r="B74">
         <v>-3.364655494689941</v>
       </c>
-      <c r="E74" t="s">
-        <v>171</v>
-      </c>
-      <c r="F74" t="s">
-        <v>182</v>
-      </c>
-      <c r="G74">
-        <f t="shared" si="1"/>
-        <v>0.30417474768994079</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>369</v>
-      </c>
-      <c r="B75" t="s">
-        <v>145</v>
-      </c>
-      <c r="C75">
         <v>-2.2564902349999998</v>
       </c>
-      <c r="D75">
+      <c r="B75">
         <v>-3.0027763843536381</v>
       </c>
-      <c r="E75" t="s">
-        <v>169</v>
-      </c>
-      <c r="F75" t="s">
-        <v>181</v>
-      </c>
-      <c r="G75">
-        <f t="shared" si="1"/>
-        <v>0.74628614935363835</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>370</v>
-      </c>
-      <c r="B76" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76">
         <v>-3.5528419690000002</v>
       </c>
-      <c r="D76">
+      <c r="B76">
         <v>-3.336361408233643</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F76" t="s">
-        <v>182</v>
-      </c>
-      <c r="G76">
-        <f t="shared" si="1"/>
-        <v>0.21648056076635713</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>374</v>
-      </c>
-      <c r="B77" t="s">
-        <v>147</v>
-      </c>
-      <c r="C77">
         <v>-4.5301779839999998</v>
       </c>
-      <c r="D77">
+      <c r="B77">
         <v>-4.8287472724914551</v>
       </c>
-      <c r="E77" t="s">
-        <v>171</v>
-      </c>
-      <c r="F77" t="s">
-        <v>182</v>
-      </c>
-      <c r="G77">
-        <f t="shared" si="1"/>
-        <v>0.29856928849145525</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>375</v>
-      </c>
-      <c r="B78" t="s">
-        <v>147</v>
-      </c>
-      <c r="C78">
         <v>-4.8860566480000003</v>
       </c>
-      <c r="D78">
+      <c r="B78">
         <v>-4.8487548828125</v>
       </c>
-      <c r="E78" t="s">
-        <v>171</v>
-      </c>
-      <c r="F78" t="s">
-        <v>182</v>
-      </c>
-      <c r="G78">
-        <f t="shared" si="1"/>
-        <v>3.730176518750028E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>376</v>
-      </c>
-      <c r="B79" t="s">
-        <v>147</v>
-      </c>
-      <c r="C79">
         <v>-4.7721132949999996</v>
       </c>
-      <c r="D79">
+      <c r="B79">
         <v>-4.8487548828125</v>
       </c>
-      <c r="E79" t="s">
-        <v>171</v>
-      </c>
-      <c r="F79" t="s">
-        <v>182</v>
-      </c>
-      <c r="G79">
-        <f t="shared" si="1"/>
-        <v>7.6641587812500411E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>379</v>
-      </c>
-      <c r="B80" t="s">
-        <v>148</v>
-      </c>
-      <c r="C80">
         <v>-5.6575773189999996</v>
       </c>
-      <c r="D80">
+      <c r="B80">
         <v>-5.6744880676269531</v>
       </c>
-      <c r="E80" t="s">
-        <v>171</v>
-      </c>
-      <c r="F80" t="s">
-        <v>182</v>
-      </c>
-      <c r="G80">
-        <f t="shared" si="1"/>
-        <v>1.691074862695352E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>381</v>
-      </c>
-      <c r="B81" t="s">
-        <v>149</v>
-      </c>
-      <c r="C81">
         <v>-5.8218212950000003</v>
       </c>
-      <c r="D81">
+      <c r="B81">
         <v>-7.7273216247558594</v>
       </c>
-      <c r="E81" t="s">
-        <v>179</v>
-      </c>
-      <c r="F81" t="s">
-        <v>183</v>
-      </c>
-      <c r="G81">
-        <f t="shared" si="1"/>
-        <v>1.905500329755859</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>388</v>
-      </c>
-      <c r="B82" t="s">
-        <v>150</v>
-      </c>
-      <c r="C82">
         <v>-3.7258421510000002</v>
       </c>
-      <c r="D82">
+      <c r="B82">
         <v>-4.5353813171386719</v>
       </c>
-      <c r="E82" t="s">
-        <v>171</v>
-      </c>
-      <c r="F82" t="s">
-        <v>182</v>
-      </c>
-      <c r="G82">
-        <f t="shared" si="1"/>
-        <v>0.80953916613867172</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>397</v>
-      </c>
-      <c r="B83" t="s">
-        <v>151</v>
-      </c>
-      <c r="C83">
         <v>-2.4584207560000002</v>
       </c>
-      <c r="D83">
+      <c r="B83">
         <v>-2.4974362850189209</v>
       </c>
-      <c r="E83" t="s">
-        <v>169</v>
-      </c>
-      <c r="F83" t="s">
-        <v>181</v>
-      </c>
-      <c r="G83">
-        <f t="shared" si="1"/>
-        <v>3.9015529018920692E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>398</v>
-      </c>
-      <c r="B84" t="s">
-        <v>152</v>
-      </c>
-      <c r="C84">
         <v>-2.521433504</v>
       </c>
-      <c r="D84">
+      <c r="B84">
         <v>-2.504153728485107</v>
       </c>
-      <c r="E84" t="s">
-        <v>169</v>
-      </c>
-      <c r="F84" t="s">
-        <v>181</v>
-      </c>
-      <c r="G84">
-        <f t="shared" si="1"/>
-        <v>1.7279775514893014E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>399</v>
-      </c>
-      <c r="B85" t="s">
-        <v>153</v>
-      </c>
-      <c r="C85">
         <v>-2.555955204</v>
       </c>
-      <c r="D85">
+      <c r="B85">
         <v>-2.473006010055542</v>
       </c>
-      <c r="E85" t="s">
-        <v>169</v>
-      </c>
-      <c r="F85" t="s">
-        <v>181</v>
-      </c>
-      <c r="G85">
-        <f t="shared" si="1"/>
-        <v>8.2949193944457988E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>400</v>
-      </c>
-      <c r="B86" t="s">
-        <v>154</v>
-      </c>
-      <c r="C86">
         <v>-2.571865206</v>
       </c>
-      <c r="D86">
+      <c r="B86">
         <v>-2.5282289981842041</v>
       </c>
-      <c r="E86" t="s">
-        <v>169</v>
-      </c>
-      <c r="F86" t="s">
-        <v>181</v>
-      </c>
-      <c r="G86">
-        <f t="shared" si="1"/>
-        <v>4.3636207815795913E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>401</v>
-      </c>
-      <c r="B87" t="s">
-        <v>155</v>
-      </c>
-      <c r="C87">
         <v>-2.4388986159999999</v>
       </c>
-      <c r="D87">
+      <c r="B87">
         <v>-2.574008703231812</v>
       </c>
-      <c r="E87" t="s">
-        <v>169</v>
-      </c>
-      <c r="F87" t="s">
-        <v>181</v>
-      </c>
-      <c r="G87">
-        <f t="shared" si="1"/>
-        <v>0.13511008723181206</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>402</v>
-      </c>
-      <c r="B88" t="s">
-        <v>156</v>
-      </c>
-      <c r="C88">
         <v>-2.4412914290000001</v>
       </c>
-      <c r="D88">
+      <c r="B88">
         <v>-2.5693972110748291</v>
       </c>
-      <c r="E88" t="s">
-        <v>169</v>
-      </c>
-      <c r="F88" t="s">
-        <v>181</v>
-      </c>
-      <c r="G88">
-        <f t="shared" si="1"/>
-        <v>0.12810578207482903</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>404</v>
-      </c>
-      <c r="B89" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89">
         <v>-2.4948500220000001</v>
       </c>
-      <c r="D89">
+      <c r="B89">
         <v>-2.6120254993438721</v>
       </c>
-      <c r="E89" t="s">
-        <v>169</v>
-      </c>
-      <c r="F89" t="s">
-        <v>181</v>
-      </c>
-      <c r="G89">
-        <f t="shared" si="1"/>
-        <v>0.11717547734387201</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>405</v>
-      </c>
-      <c r="B90" t="s">
-        <v>158</v>
-      </c>
-      <c r="C90">
         <v>-2.442492798</v>
       </c>
-      <c r="D90">
+      <c r="B90">
         <v>-2.7709224224090581</v>
       </c>
-      <c r="E90" t="s">
-        <v>169</v>
-      </c>
-      <c r="F90" t="s">
-        <v>181</v>
-      </c>
-      <c r="G90">
-        <f t="shared" si="1"/>
-        <v>0.3284296244090581</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>408</v>
-      </c>
-      <c r="B91" t="s">
-        <v>159</v>
-      </c>
-      <c r="C91">
         <v>-3.1542819820000001</v>
       </c>
-      <c r="D91">
+      <c r="B91">
         <v>-3.2165474891662602</v>
       </c>
-      <c r="E91" t="s">
-        <v>169</v>
-      </c>
-      <c r="F91" t="s">
-        <v>181</v>
-      </c>
-      <c r="G91">
-        <f t="shared" si="1"/>
-        <v>6.2265507166260115E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>409</v>
-      </c>
-      <c r="B92" t="s">
-        <v>159</v>
-      </c>
-      <c r="C92">
         <v>-2.5575202309999998</v>
       </c>
-      <c r="D92">
+      <c r="B92">
         <v>-3.1761713027954102</v>
       </c>
-      <c r="E92" t="s">
-        <v>169</v>
-      </c>
-      <c r="F92" t="s">
-        <v>181</v>
-      </c>
-      <c r="G92">
-        <f t="shared" si="1"/>
-        <v>0.61865107179541035</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>413</v>
-      </c>
-      <c r="B93" t="s">
-        <v>160</v>
-      </c>
-      <c r="C93">
         <v>-3.9507819770000001</v>
       </c>
-      <c r="D93">
+      <c r="B93">
         <v>-2.9297201633453369</v>
       </c>
-      <c r="E93" t="s">
-        <v>169</v>
-      </c>
-      <c r="F93" t="s">
-        <v>181</v>
-      </c>
-      <c r="G93">
-        <f t="shared" si="1"/>
-        <v>1.0210618136546632</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>418</v>
-      </c>
-      <c r="B94" t="s">
-        <v>161</v>
-      </c>
-      <c r="C94">
         <v>-2.645891561</v>
       </c>
-      <c r="D94">
+      <c r="B94">
         <v>-3.5753614902496338</v>
       </c>
-      <c r="E94" t="s">
-        <v>169</v>
-      </c>
-      <c r="F94" t="s">
-        <v>181</v>
-      </c>
-      <c r="G94">
-        <f t="shared" si="1"/>
-        <v>0.92946992924963379</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>420</v>
-      </c>
-      <c r="B95" t="s">
-        <v>162</v>
-      </c>
-      <c r="C95">
         <v>-3.657577319</v>
       </c>
-      <c r="D95">
+      <c r="B95">
         <v>-5.4947185516357422</v>
       </c>
-      <c r="E95" t="s">
-        <v>169</v>
-      </c>
-      <c r="F95" t="s">
-        <v>181</v>
-      </c>
-      <c r="G95">
-        <f t="shared" si="1"/>
-        <v>1.8371412326357421</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>421</v>
-      </c>
-      <c r="B96" t="s">
-        <v>162</v>
-      </c>
-      <c r="C96">
         <v>-5.8996294550000004</v>
       </c>
-      <c r="D96">
+      <c r="B96">
         <v>-5.4947185516357422</v>
       </c>
-      <c r="E96" t="s">
-        <v>169</v>
-      </c>
-      <c r="F96" t="s">
-        <v>181</v>
-      </c>
-      <c r="G96">
-        <f t="shared" si="1"/>
-        <v>0.40491090336425817</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>433</v>
-      </c>
-      <c r="B97" t="s">
-        <v>163</v>
-      </c>
-      <c r="C97">
         <v>-5.7878123959999996</v>
       </c>
-      <c r="D97">
+      <c r="B97">
         <v>-4.4108428955078116</v>
       </c>
-      <c r="E97" t="s">
-        <v>171</v>
-      </c>
-      <c r="F97" t="s">
-        <v>182</v>
-      </c>
-      <c r="G97">
-        <f t="shared" si="1"/>
-        <v>1.376969500492188</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>434</v>
-      </c>
-      <c r="B98" t="s">
-        <v>163</v>
-      </c>
-      <c r="C98">
         <v>-5.7055337740000001</v>
       </c>
-      <c r="D98">
+      <c r="B98">
         <v>-4.0763978958129883</v>
       </c>
-      <c r="E98" t="s">
-        <v>171</v>
-      </c>
-      <c r="F98" t="s">
-        <v>182</v>
-      </c>
-      <c r="G98">
-        <f t="shared" si="1"/>
-        <v>1.6291358781870118</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>438</v>
-      </c>
-      <c r="B99" t="s">
-        <v>164</v>
-      </c>
-      <c r="C99">
         <v>-4.0655015490000004</v>
       </c>
-      <c r="D99">
+      <c r="B99">
         <v>-4.6332731246948242</v>
       </c>
-      <c r="E99" t="s">
-        <v>178</v>
-      </c>
-      <c r="F99" t="s">
-        <v>183</v>
-      </c>
-      <c r="G99">
-        <f t="shared" si="1"/>
-        <v>0.56777157569482384</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>441</v>
-      </c>
-      <c r="B100" t="s">
-        <v>165</v>
-      </c>
-      <c r="C100">
         <v>-2.2596373110000001</v>
       </c>
-      <c r="D100">
+      <c r="B100">
         <v>-2.218172550201416</v>
       </c>
-      <c r="E100" t="s">
-        <v>172</v>
-      </c>
-      <c r="F100" t="s">
-        <v>181</v>
-      </c>
-      <c r="G100">
-        <f t="shared" si="1"/>
-        <v>4.1464760798584077E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>469</v>
-      </c>
-      <c r="B101" t="s">
-        <v>166</v>
-      </c>
-      <c r="C101">
         <v>-8.316052869</v>
       </c>
-      <c r="D101">
+      <c r="B101">
         <v>-6.5854721069335938</v>
       </c>
-      <c r="E101" t="s">
-        <v>175</v>
-      </c>
-      <c r="F101" t="s">
-        <v>182</v>
-      </c>
-      <c r="G101">
-        <f t="shared" si="1"/>
-        <v>1.7305807620664062</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>492</v>
-      </c>
-      <c r="B102" t="s">
-        <v>167</v>
-      </c>
-      <c r="C102">
         <v>-6.4168012259999996</v>
       </c>
-      <c r="D102">
+      <c r="B102">
         <v>-4.0695204734802246</v>
       </c>
-      <c r="E102" t="s">
-        <v>175</v>
-      </c>
-      <c r="F102" t="s">
-        <v>182</v>
-      </c>
-      <c r="G102">
-        <f t="shared" si="1"/>
-        <v>2.347280752519775</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F102">
-      <sortCondition ref="B1"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="A1:A102">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>2.4547653738409281E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>1.132339797914028E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1.6315465793013569E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>7.6413331553339958E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>3.3237903844565149E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>7.9128757119178772E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>3.1289537437260151E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>4.0170862339437008E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>4.7032511793076992E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>3.2532796263694763E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>1.3011588016524911E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <v>3.666000440716743E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>2.3810742422938351E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
-        <v>2.5700835511088371E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
-        <v>1.2063366360962389E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17">
-        <v>1.150556281208992E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18">
-        <v>6.4080539159476757E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19">
-        <v>1.3360244920477271E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20">
-        <v>2.2183345630764961E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21">
-        <v>2.193505130708218E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
-        <v>1.5710456296801571E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23">
-        <v>1.948892883956432E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24">
-        <v>7.7387765049934387E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25">
-        <v>2.6573606301099062E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26">
-        <v>5.7403232902288437E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27">
-        <v>3.2765995711088181E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28">
-        <v>8.233098778873682E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29">
-        <v>3.706708550453186E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30">
-        <v>5.7976096868515006E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31">
-        <v>1.4105763286352159E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32">
-        <v>7.3813535273075104E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33">
-        <v>4.3154424056410789E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34">
-        <v>7.2757839225232601E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35">
-        <v>2.505169482901692E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36">
-        <v>2.6518476661294699E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37">
-        <v>7.2961725294589996E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38">
-        <v>2.7749070897698399E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40">
-        <v>1.573265762999654E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41">
-        <v>4.6616408973932273E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42">
-        <v>8.15543532371521E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43">
-        <v>6.5989559516310692E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44">
-        <v>2.251331880688667E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45">
-        <v>9.6525270491838455E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46">
-        <v>7.5601786375045776E-4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47">
-        <v>1.1429563164711E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48">
-        <v>7.5958877801895142E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>53</v>
-      </c>
-      <c r="B49">
-        <v>4.95634526014328E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50">
-        <v>8.5020915139466524E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51">
-        <v>4.0902849286794662E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52">
-        <v>8.5311029106378555E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53">
-        <v>4.302408080548048E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54">
-        <v>1.5191724523901939E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55">
-        <v>3.9894385263323784E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>60</v>
-      </c>
-      <c r="B56">
-        <v>2.7635611593723301E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57">
-        <v>1.582019962370396E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>62</v>
-      </c>
-      <c r="B58">
-        <v>1.8191637471318241E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59">
-        <v>1.118761207908392E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60">
-        <v>2.7475204318761829E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>65</v>
-      </c>
-      <c r="B61">
-        <v>3.5015568137168877E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
